--- a/credito_original.xlsx
+++ b/credito_original.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisb\Desktop\Trabalho_P4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66468D8A-0645-4576-BEDC-E30119E1892F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2C45BB-6FDA-4629-B1EE-5245D7C6A96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3030" yWindow="3030" windowWidth="21600" windowHeight="11385" xr2:uid="{C5FFC5E2-503E-4BC0-A6EF-3B3CC968B4FB}"/>
   </bookViews>
@@ -39,16 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>A — Cliente</t>
-  </si>
-  <si>
-    <t>B — Rendimento (€)</t>
-  </si>
-  <si>
-    <t>C — Dívida (€)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Cliente</t>
   </si>
@@ -78,7 +69,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,31 +78,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -141,12 +119,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -483,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB7FAA25-C5B2-49CE-97C3-5337E54A6585}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.7109375" customWidth="1"/>
@@ -491,7 +466,7 @@
     <col min="3" max="3" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -502,69 +477,58 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C2" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="1">
+        <v>800</v>
+      </c>
+      <c r="C3" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B4" s="1">
+        <v>3500</v>
+      </c>
+      <c r="C4" s="1">
+        <v>800</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
-        <v>2000</v>
-      </c>
-      <c r="C3" s="2">
-        <v>400</v>
+      <c r="B5" s="1">
+        <v>1200</v>
+      </c>
+      <c r="C5" s="1">
+        <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
-        <v>800</v>
-      </c>
-      <c r="C4" s="2">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2">
-        <v>3500</v>
-      </c>
-      <c r="C5" s="2">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1200</v>
-      </c>
-      <c r="C6" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="B6" s="1">
         <v>950</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C6" s="1">
         <v>600</v>
       </c>
     </row>
